--- a/output/pdf_financials_xlsx/GPUS.xlsx
+++ b/output/pdf_financials_xlsx/GPUS.xlsx
@@ -5912,49 +5912,49 @@
         <v>0.620279</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.604504</v>
+        <v>0.201644</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1.039183</v>
+        <v>0.506787</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.5380470000000001</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.535102</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.591521</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.5426029999999999</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.200179</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.322465</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.135336</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.458056</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.459942</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.499971</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.499971</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.605097</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.278525</v>
       </c>
     </row>
     <row r="93">
@@ -10191,7 +10191,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11615,7 +11619,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -13425,7 +13433,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14938,7 +14950,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16663,7 +16679,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -17778,7 +17798,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18699,7 +18723,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -19709,7 +19737,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GPUS.xlsx
+++ b/output/pdf_financials_xlsx/GPUS.xlsx
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005847</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011143</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.242019</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.036365</v>
       </c>
     </row>
     <row r="13">
@@ -1977,10 +1977,10 @@
         <v>-0.310579</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.026329</v>
+        <v>-1.032176</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.661212</v>
+        <v>-0.650069</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.251537</v>
@@ -2016,10 +2016,10 @@
         <v>-0.256708</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-6.349021</v>
+        <v>-6.59104</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-7.025616</v>
+        <v>-7.061981</v>
       </c>
     </row>
     <row r="28">
@@ -2093,10 +2093,10 @@
         <v>-0.310579</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.026329</v>
+        <v>-1.032176</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.660544</v>
+        <v>-0.649401</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.250008</v>
@@ -2132,10 +2132,10 @@
         <v>-0.256708</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-6.349021</v>
+        <v>-6.59104</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-7.025616</v>
+        <v>-7.061981</v>
       </c>
     </row>
     <row r="30">
@@ -2151,10 +2151,10 @@
         <v>-63.63958625324776</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-178.2387459904796</v>
+        <v>-179.254172766695</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-117.7450779418711</v>
+        <v>-115.7587857289281</v>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
@@ -2370,28 +2370,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.112261</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.407802</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.106342</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.400078</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.110623</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000861</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.012068</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.008880000000000001</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.005487</v>
@@ -2406,19 +2406,19 @@
         <v>0.014164</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000686</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.41952</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.147656</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.797575</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.7382</v>
       </c>
     </row>
     <row r="35">
@@ -2486,28 +2486,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.112261</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.407802</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.106342</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.400078</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.032913</v>
+        <v>0.143536</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000861</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.012068</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.008880000000000001</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>0.005487</v>
@@ -2522,19 +2522,19 @@
         <v>0.014164</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000686</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.41952</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.147656</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.797575</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.7382</v>
       </c>
     </row>
     <row r="37">
@@ -3182,28 +3182,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.114366</v>
+        <v>0.002105</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.418008</v>
+        <v>0.010206</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.212056</v>
+        <v>0.105714</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.407911</v>
+        <v>0.007833</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.159539</v>
+        <v>0.048916</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008189999999999999</v>
+        <v>0.007329</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.016268</v>
+        <v>0.0042</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.010085</v>
+        <v>0.001205</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.002835</v>
@@ -3218,19 +3218,19 @@
         <v>0.005276</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.000686</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.420363</v>
+        <v>0.000843</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.148436</v>
+        <v>0.00078</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.031821</v>
+        <v>0.234246</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.785189</v>
+        <v>0.046989</v>
       </c>
     </row>
     <row r="49">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -53955,7 +53955,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -54749,7 +54749,7 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
@@ -60038,7 +60038,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -65042,7 +65042,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -67244,7 +67244,7 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">

--- a/output/pdf_financials_xlsx/GPUS.xlsx
+++ b/output/pdf_financials_xlsx/GPUS.xlsx
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.000338</v>
+        <v>0.007224</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.024264</v>
@@ -70072,7 +70072,11 @@
           <t>Occupancy costs (Note 8)</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr"/>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E613" s="5" t="n">
         <v>0.006886</v>
       </c>

--- a/output/pdf_financials_xlsx/GPUS.xlsx
+++ b/output/pdf_financials_xlsx/GPUS.xlsx
@@ -1285,13 +1285,13 @@
         <v>-1.595542</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-1.320455</v>
+        <v>-1.295455</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-2.28374</v>
+        <v>-2.26374</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-13.519238</v>
+        <v>-13.464238</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>-0.931393</v>
@@ -1343,13 +1343,13 @@
         <v>-0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.025</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.02</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.055</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -1569,11 +1569,15 @@
       <c r="D20" s="3" t="n">
         <v>-1.026329</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.661212</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-1.251537</v>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
         <v>-1.963908</v>
@@ -1628,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.06673</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.209616</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1995,13 +1999,13 @@
         <v>-1.595542</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.320455</v>
+        <v>-1.295455</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.28374</v>
+        <v>-2.26374</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-13.519238</v>
+        <v>-13.464238</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.931393</v>
@@ -2111,13 +2115,13 @@
         <v>-1.594686</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.320455</v>
+        <v>-1.295455</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.28374</v>
+        <v>-2.26374</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-13.519238</v>
+        <v>-13.464238</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.931393</v>
@@ -2187,7 +2191,7 @@
         </is>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-5445.09209249123</v>
+        <v>-5422.939951587503</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-436.0494948454574</v>
@@ -2249,13 +2253,13 @@
         <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.929823884272321</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.8834936874376034</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.408489511251955</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>-0</v>
@@ -6974,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.003343</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.000681</v>
       </c>
     </row>
     <row r="111">
@@ -6990,7 +6994,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002675</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6999,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003433</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -7017,7 +7021,7 @@
         <v>-0.005464</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.020776</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -7267,7 +7271,7 @@
         <v>0</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.528316</v>
       </c>
     </row>
     <row r="116">
@@ -8368,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002675</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8377,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003433</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -8395,7 +8399,7 @@
         <v>-0.005464</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020776</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -8426,7 +8430,7 @@
         <v>0.010353</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.07886899999999999</v>
+        <v>-0.08154400000000001</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.222359</v>
@@ -8435,7 +8439,7 @@
         <v>-0.291115</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.040826</v>
+        <v>-1.044259</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
@@ -23500,7 +23504,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -24791,7 +24799,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -25672,7 +25684,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -30120,7 +30136,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -34059,7 +34079,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -35839,7 +35863,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -40315,7 +40343,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -46061,7 +46093,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -50192,7 +50228,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -52531,7 +52571,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -59244,7 +59288,11 @@
           <t>Deferred income tax recovery 18</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -60737,7 +60785,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -62438,7 +62490,11 @@
           <t>Deferred income tax recovery (Note 17)</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr"/>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E537" t="inlineStr">
         <is>
           <t>-</t>
@@ -64939,7 +64995,11 @@
           <t>Loss from discontinued operations (Note 4)</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr"/>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E562" t="inlineStr">
         <is>
           <t>-</t>
@@ -65343,7 +65403,11 @@
           <t>Net (loss) gain from discontinued operations (Note 4)</t>
         </is>
       </c>
-      <c r="D566" t="inlineStr"/>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E566" t="inlineStr">
         <is>
           <t>-</t>
